--- a/import-templates/import-template-service-contracts.xlsx
+++ b/import-templates/import-template-service-contracts.xlsx
@@ -50,7 +50,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -72,6 +72,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF3F4F6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB45309"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -103,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -127,6 +133,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -160,7 +169,7 @@
           <t xml:space="preserve">title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">customer_code</t>
         </is>
@@ -257,7 +266,7 @@
           <t xml:space="preserve">title</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">customer_code</t>
         </is>
@@ -536,7 +545,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">หัวคอลัมน์สีส้ม = จำเป็นต้องกรอก / สีเขียว = ไม่บังคับ (เว้นว่างได้)</t>
+          <t xml:space="preserve">หัวคอลัมน์สีส้ม = จำเป็นต้องกรอก / สีเหลือง = ไม่บังคับ แต่แนะนำอย่างยิ่ง / สีเขียว = เว้นว่างได้</t>
         </is>
       </c>
     </row>
@@ -643,7 +652,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">แนะนำ</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">

--- a/import-templates/import-template-service-contracts.xlsx
+++ b/import-templates/import-template-service-contracts.xlsx
@@ -146,21 +146,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1" style="3"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1" style="3"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1" style="3"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -171,70 +172,75 @@
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">tax_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">customer_code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">company_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">site_name</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">service_type</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">start_date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">frequency_per_year</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">duration_years</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">technician_name</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">board_key</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L1"/>
+  <autoFilter ref="A1:M1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="E2:E2000">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="F2:F2000">
       <formula1>"panel_cleaning,filter_cleaning,inspection,maintenance,other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="J2:J2000">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="K2:K2000">
       <formula1>"unigreen,product_sales,services_sales"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="K2:K2000">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="ค่าไม่ถูกต้อง" error="กรุณาเลือกจากรายการที่กำหนด" sqref="L2:L2000">
       <formula1>"active,completed,cancelled"</formula1>
     </dataValidation>
   </dataValidations>
@@ -243,21 +249,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="30" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="16" customWidth="1"/>
+    <col min="12" max="12" width="13" customWidth="1"/>
+    <col min="13" max="13" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -268,55 +275,60 @@
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">tax_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">customer_code</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">company_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">site_name</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">service_type</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">start_date</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">frequency_per_year</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">duration_years</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">technician_name</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">board_key</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">status</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
@@ -325,60 +337,65 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">สัญญาล้างแผง โรงงานบางปู 5 ปี</t>
+          <t xml:space="preserve">สัญญาล้างแผง PT บางปู 5 ปี</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-00142</t>
+          <t xml:space="preserve">0105536000123</t>
         </is>
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">บริษัท ไทยรุ่งเรือง จำกัด</t>
+          <t xml:space="preserve">GS20260012</t>
         </is>
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">โรงงานบางปู เฟส 2</t>
+          <t xml:space="preserve">บริษัท ไทยรุ่งเรือง ปิโตรเลียม จำกัด</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">PT บางปู สมุทรปราการ</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">panel_cleaning</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-01-15</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">อนุชา พรมมา</t>
-        </is>
-      </c>
       <c r="J2" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">ธนวัฒน์</t>
+        </is>
+      </c>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">unigreen</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">active</t>
         </is>
       </c>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">ราคาเหมารวมค่าน้ำ</t>
         </is>
@@ -387,60 +404,61 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">สัญญา PM ระบบโซลาร์ ลาดกระบัง</t>
+          <t xml:space="preserve">สัญญา PM ระบบไฟฟ้า ลาดกระบัง</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">C-00187</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">บริษัท เอ็นเนอร์ยี่ พลัส จำกัด</t>
-        </is>
-      </c>
+          <t xml:space="preserve">0105551000456</t>
+        </is>
+      </c>
+      <c r="C3" s="9"/>
       <c r="D3" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">ห้างหุ้นส่วนจำกัด เอ็นเนอร์ยี่ พลัส</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">คลังสินค้าลาดกระบัง</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">maintenance</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-01</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ธนพล แก้วมณี</t>
-        </is>
-      </c>
       <c r="J3" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">เฉลิมเกียรติ ศรีสว่าง</t>
+        </is>
+      </c>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">services_sales</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">active</t>
         </is>
       </c>
-      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
@@ -449,48 +467,49 @@
         </is>
       </c>
       <c r="B4" s="9"/>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">บริษัท ไทยรุ่งเรือง จำกัด</t>
-        </is>
-      </c>
+      <c r="C4" s="9"/>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">สาขาระยอง (หลังคาอาคาร A)</t>
+          <t xml:space="preserve">บริษัท สุขสบาย เซอร์วิส จำกัด</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
+          <t xml:space="preserve">สาขาระยอง (อาคาร A)</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
           <t xml:space="preserve">filter_cleaning</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2025-09-01</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">2.5</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="9"/>
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">product_sales</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">active</t>
         </is>
       </c>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">เริ่มหลังส่งมอบงานติดตั้ง</t>
         </is>
@@ -510,7 +529,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -559,127 +578,87 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ไม่มีคอลัมน์ end_date — ระบบคำนวณให้เอง = start_date + (duration_years × 12) เดือน</t>
+          <t xml:space="preserve">ลำดับการจับคู่บริษัท: customer_code → tax_id → company_name</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">รอบเข้าบริการ (service_visits) ระบบสร้างให้อัตโนมัติ = frequency_per_year × duration_years รอบ</t>
+          <t xml:space="preserve">ช่างในระบบบางคนมีแต่ชื่อไม่มีนามสกุล (เช่น “ธนวัฒน์”) — technician_name ต้องสะกดตรงกับที่มีในระบบ</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  เช่น 2 ครั้ง/ปี × 5 ปี = 10 รอบ ห่างกันรอบละ 6 เดือน นับจาก start_date</t>
+          <t xml:space="preserve">ไม่มีคอลัมน์ end_date — ระบบคำนวณให้เอง = start_date + (duration_years × 12) เดือน</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">รอบเข้าบริการ (service_visits) ระบบสร้างให้อัตโนมัติ = frequency_per_year × duration_years รอบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  เช่น 2 ครั้ง/ปี × 5 ปี = 10 รอบ ห่างกันรอบละ 6 เดือน นับจาก start_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">ช่องวันที่เป็นรูปแบบข้อความ YYYY-MM-DD เช่น 2026-03-15 (ตั้งค่าคอลัมน์เป็น Text ไว้ให้แล้ว)</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="13"/>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">คอลัมน์</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ชื่อหัวคอลัมน์</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">จำเป็น</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">ชนิดข้อมูล</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">คำอธิบาย</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">title</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ใช่</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ข้อความ</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ชื่อสัญญา เช่น “สัญญาล้างแผง โรงงานบางปู 5 ปี”</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">B</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">customer_code</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">แนะนำ</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ข้อความ</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">รหัสลูกค้า — วิธีจับคู่บริษัทที่แม่นที่สุด ใช้ก่อน company_name</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">C</t>
+          <t xml:space="preserve">A</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">company_name</t>
+          <t xml:space="preserve">title</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">ใช่</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -689,24 +668,24 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชื่อบริษัทคู่สัญญา — ใช้เมื่อไม่ได้ใส่ customer_code</t>
+          <t xml:space="preserve">ชื่อสัญญา เช่น “สัญญาล้างแผง โรงงานบางปู 5 ปี”</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">D</t>
+          <t xml:space="preserve">B</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">site_name</t>
+          <t xml:space="preserve">tax_id</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">แนะนำ</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -716,73 +695,73 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชื่อไซต์งานที่เข้าบริการ ต้องสะกดตรงกับไซต์ที่มีในระบบ</t>
+          <t xml:space="preserve">เลขผู้เสียภาษีของบริษัทคู่สัญญา — วิธีจับคู่ที่ครอบคลุมที่สุดสำหรับลูกค้าเดิม</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">E</t>
+          <t xml:space="preserve">C</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">service_type</t>
+          <t xml:space="preserve">customer_code</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใช่</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตัวเลือก: panel_cleaning / filter_cleaning / inspection / maintenance / other</t>
+          <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ประเภทงาน: panel_cleaning = ล้างแผงโซลาร์, filter_cleaning = ล้างฟิลเตอร์ (EV), inspection = ตรวจเช็กระบบ, maintenance = บำรุงรักษา, other = อื่นๆ · เว้นว่าง = panel_cleaning</t>
+          <t xml:space="preserve">รหัสลูกค้าของบริษัทคู่สัญญา — ถ้ากรอกจะใช้จับคู่ก่อน tax_id</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">F</t>
+          <t xml:space="preserve">D</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">start_date</t>
+          <t xml:space="preserve">company_name</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ใช่</t>
+          <t xml:space="preserve">—</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">วันที่ YYYY-MM-DD</t>
+          <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">วันเริ่มสัญญา — ใช้เป็นจุดตั้งต้นของทุกรอบเข้าบริการ</t>
+          <t xml:space="preserve">ชื่อบริษัทคู่สัญญา — ใช้เมื่อไม่ได้ใส่ทั้ง customer_code และ tax_id</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">G</t>
+          <t xml:space="preserve">E</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">frequency_per_year</t>
+          <t xml:space="preserve">site_name</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -792,78 +771,78 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">จำนวนเต็ม</t>
+          <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">จำนวนครั้งที่เข้าบริการต่อปี เช่น 2 = ทุก 6 เดือน, 4 = ทุก 3 เดือน · เว้นว่าง = 2</t>
+          <t xml:space="preserve">ชื่อไซต์งานที่เข้าบริการ ต้องสะกดตรงกับไซต์ที่มีในระบบ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">H</t>
+          <t xml:space="preserve">F</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">duration_years</t>
+          <t xml:space="preserve">service_type</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">ใช่</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตัวเลข</t>
+          <t xml:space="preserve">ตัวเลือก: panel_cleaning / filter_cleaning / inspection / maintenance / other</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">อายุสัญญาเป็นปี ใส่ทศนิยม 1 ตำแหน่งได้ เช่น 2.5 · เว้นว่าง = 5</t>
+          <t xml:space="preserve">ประเภทงาน: panel_cleaning = ล้างแผงโซลาร์, filter_cleaning = ล้างฟิลเตอร์ (EV), inspection = ตรวจเช็กระบบ, maintenance = บำรุงรักษา, other = อื่นๆ · เว้นว่าง = panel_cleaning</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">I</t>
+          <t xml:space="preserve">G</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">technician_name</t>
+          <t xml:space="preserve">start_date</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">—</t>
+          <t xml:space="preserve">ใช่</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ข้อความ</t>
+          <t xml:space="preserve">วันที่ YYYY-MM-DD</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ชื่อช่างผู้รับผิดชอบ ต้องตรงกับรายชื่อช่างในระบบ</t>
+          <t xml:space="preserve">วันเริ่มสัญญา — ใช้เป็นจุดตั้งต้นของทุกรอบเข้าบริการ</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">J</t>
+          <t xml:space="preserve">H</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">board_key</t>
+          <t xml:space="preserve">frequency_per_year</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -873,24 +852,24 @@
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตัวเลือก: unigreen / product_sales / services_sales</t>
+          <t xml:space="preserve">จำนวนเต็ม</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">แผนก/บอร์ดที่ดูแลสัญญานี้ · ค่าที่ไม่อยู่ในรายการจะถูกล้างเป็นว่าง</t>
+          <t xml:space="preserve">จำนวนครั้งที่เข้าบริการต่อปี เช่น 2 = ทุก 6 เดือน, 4 = ทุก 3 เดือน · เว้นว่าง = 2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">K</t>
+          <t xml:space="preserve">I</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">status</t>
+          <t xml:space="preserve">duration_years</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -900,37 +879,118 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ตัวเลือก: active / completed / cancelled</t>
+          <t xml:space="preserve">ตัวเลข</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">สถานะสัญญา: active = ใช้งานอยู่, completed = จบสัญญา, cancelled = ยกเลิก · เว้นว่าง = active</t>
+          <t xml:space="preserve">อายุสัญญาเป็นปี ใส่ทศนิยม 1 ตำแหน่งได้ เช่น 2.5 · เว้นว่าง = 5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">J</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">technician_name</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ข้อความ</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ชื่อช่างผู้รับผิดชอบ ต้องตรงกับรายชื่อช่างในระบบ</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">K</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">board_key</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ตัวเลือก: unigreen / product_sales / services_sales</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">แผนก/บอร์ดที่ดูแลสัญญานี้ · ค่าที่ไม่อยู่ในรายการจะถูกล้างเป็นว่าง</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">L</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">status</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">—</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ตัวเลือก: active / completed / cancelled</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">สถานะสัญญา: active = ใช้งานอยู่, completed = จบสัญญา, cancelled = ยกเลิก · เว้นว่าง = active</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">notes</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">—</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">ข้อความ</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">หมายเหตุ เช่น เงื่อนไขราคา หรือข้อตกลงพิเศษ</t>
         </is>
